--- a/public/outils/matrices/avis-de-valeur-par-comparaison.xlsx
+++ b/public/outils/matrices/avis-de-valeur-par-comparaison.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="446">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -51,7 +51,7 @@
     <t>Il calcule le prix au m² de chaque vente comparable, puis lui applique une grille d'ajustements : des corrections chiffrées qui rapprochent la vente du bien à évaluer (état, étage, extérieur, étiquette DPE, stationnement, écoulement du temps). Il pondère ensuite chaque comparable par sa ressemblance avec le bien, puis produit une valeur centrale et une fourchette dont la largeur est mesurée sur la dispersion du panel, c'est-à-dire sur l'écart qui sépare encore les ventes retenues une fois corrigées.</t>
   </si>
   <si>
-    <t>Le classeur est livré rempli d'un exemple : un appartement de 75 m² et six ventes comparables. Pour votre dossier, remplacez les cellules bleues de l'onglet Avis de valeur. Celles du Référentiel sont vos coefficients : elles se recalent une fois par marché, jamais par dossier. L'étape 0 de la marche à suivre dit exactement lesquelles se vident, et lesquelles ne se vident jamais.</t>
+    <t>Le classeur est livré rempli d'un exemple : un appartement de 75 m² et six ventes comparables. Pour votre dossier, remplacez les cellules violettes de l'onglet Avis de valeur. Celles du Référentiel sont vos coefficients : elles se recalent une fois par marché, jamais par dossier. L'étape 0 de la marche à suivre dit exactement lesquelles se vident, et lesquelles ne se vident jamais.</t>
   </si>
   <si>
     <t>Vous êtes</t>
@@ -153,7 +153,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu ciel, texte bleu nuit</t>
+    <t>Fond violet clair, texte violet sombre</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -171,7 +171,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond presque blanc, texte bleu nuit en gras</t>
+    <t>Fond presque blanc, texte violet sombre en gras</t>
   </si>
   <si>
     <t>Résultat, chiffre clé</t>
@@ -180,7 +180,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section ou en-tête de tableau</t>
@@ -207,7 +207,7 @@
     <t>Vous le lisez. Il est verrouillé, parce que les formules testent son texte : pour le modifier, ôtez d'abord la protection de la feuille.</t>
   </si>
   <si>
-    <t>Cellule bleue qui affiche un %</t>
+    <t>Cellule violette qui affiche un %</t>
   </si>
   <si>
     <t>Coefficient</t>
@@ -243,7 +243,7 @@
     <t>Rouge (Avis de valeur!C53) : la dispersion de votre panel dépasse le seuil du Référentiel, ou l'échantillon est trop petit pour la mesurer. La fourchette reste juste, mais elle est large. Resserrez la sélection, ou écrivez au dossier pourquoi ces ventes sont les seules disponibles.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. En usage normal vous n'en avez jamais besoin : toutes les cellules bleues sont déjà libres. Pour modifier une cellule blanche ou un texte de source : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. En usage normal vous n'en avez jamais besoin : toutes les cellules violettes sont déjà libres. Pour modifier une cellule blanche ou un texte de source : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -264,7 +264,7 @@
     <t>Avis de valeur!C8:C17 et Avis de valeur!B23:K30</t>
   </si>
   <si>
-    <t>Le classeur arrive rempli d'un exemple : un appartement et six ventes. Effacez les cellules bleues du bien (Avis de valeur!C8:C17) et celles du tableau des comparables (Avis de valeur!B23:K30, soit les 6 lignes de l'exemple et les 2 lignes libres) avant de saisir votre dossier, ou gardez l'exemple pour vous repérer et travaillez à côté. Ne videz jamais les cellules du Référentiel : ce sont vos coefficients, pas des données de dossier. Vérifiez surtout les saisies d'option qui n'ont pas de raison d'être dans votre cas : extérieur (Avis de valeur!C13), stationnement (Avis de valeur!C15), ascenseur (Avis de valeur!C16), et la date de l'avis (Avis de valeur!C17), qui reste souvent celle de l'exemple. Pour supprimer une ligne de comparable, videz la ligne entière de la colonne B à la colonne K : tant qu'une seule cellule bleue y reste remplie, la ligne compte comme renseignée et bloque le calcul.</t>
+    <t>Le classeur arrive rempli d'un exemple : un appartement et six ventes. Effacez les cellules violettes du bien (Avis de valeur!C8:C17) et celles du tableau des comparables (Avis de valeur!B23:K30, soit les 6 lignes de l'exemple et les 2 lignes libres) avant de saisir votre dossier, ou gardez l'exemple pour vous repérer et travaillez à côté. Ne videz jamais les cellules du Référentiel : ce sont vos coefficients, pas des données de dossier. Vérifiez surtout les saisies d'option qui n'ont pas de raison d'être dans votre cas : extérieur (Avis de valeur!C13), stationnement (Avis de valeur!C15), ascenseur (Avis de valeur!C16), et la date de l'avis (Avis de valeur!C17), qui reste souvent celle de l'exemple. Pour supprimer une ligne de comparable, videz la ligne entière de la colonne B à la colonne K : tant qu'une seule cellule violette y reste remplie, la ligne compte comme renseignée et bloque le calcul.</t>
   </si>
   <si>
     <t>Une valeur de l'exemple oubliée est l'erreur la plus probable d'un premier usage. Pendant que vous effacez, puis pendant que vous saisissez, les contrôles restent rouges et la valeur centrale affiche successivement Bien incomplet, Trop peu de comparables, puis Lignes à compléter : c'est normal, le classeur ne conclut qu'une fois la saisie complète, et il préfère nommer ce qui manque plutôt qu'afficher un chiffre qu'il ne tient pas. Une date d'avis restée au 16/08/2026 fera rejeter toutes vos ventes plus récentes, qui passeront à compléter, et le classeur refusera de conclure.</t>
@@ -348,7 +348,7 @@
     <t>Référentiel!C9, Référentiel!C13:D19, Référentiel!C23:C27 et Référentiel!C31:C43</t>
   </si>
   <si>
-    <t>Une fois par marché, pas une fois par dossier : comparez chaque valeur bleue à sa source (colonne D, colonne F pour la grille DPE) et mettez à jour la date en Référentiel!C56. Les mentions « Vérifié le » suivent automatiquement.</t>
+    <t>Une fois par marché, pas une fois par dossier : comparez chaque valeur violette à sa source (colonne D, colonne F pour la grille DPE) et mettez à jour la date en Référentiel!C56. Les mentions « Vérifié le » suivent automatiquement.</t>
   </si>
   <si>
     <t>Un coefficient national appliqué à un marché local est la première critique qu'on vous fera. Un référentiel visible se discute ; un coefficient caché dans une formule se subit.</t>
@@ -684,7 +684,7 @@
     <t>Cinq ventes au minimum, des ajustements explicites, une fourchette large comme la dispersion des comparables.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  LE BIEN À ÉVALUER</t>
@@ -852,7 +852,7 @@
     <t>Comparables renseignés</t>
   </si>
   <si>
-    <t>Lignes du tableau où au moins une cellule bleue est remplie.</t>
+    <t>Lignes du tableau où au moins une cellule violette est remplie.</t>
   </si>
   <si>
     <t>Ceux qui entrent réellement dans la moyenne, et eux seuls. Minimum exigé en Référentiel!C33.</t>
@@ -1402,7 +1402,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1422,19 +1422,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1446,7 +1446,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1459,12 +1459,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1474,7 +1474,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1777,6 +1777,138 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13001625" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13001625" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9991725" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9991725" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8515350" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8515350" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3096,13 +3228,14 @@
     <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF3B6EF6"/>
+    <tabColor rgb="FF6C5AB0"/>
   </sheetPr>
   <dimension ref="B1:P65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4176,6 +4309,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
@@ -4224,7 +4358,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor rgb="FFB08C4E"/>
+    <tabColor rgb="FF495669"/>
   </sheetPr>
   <dimension ref="B1:F61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4954,13 +5088,14 @@
     <mergeCell ref="B61:F61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF5A6B8C"/>
+    <tabColor rgb="FF8A93A6"/>
   </sheetPr>
   <dimension ref="B1:C58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5404,5 +5539,6 @@
     <mergeCell ref="B27:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>